--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.14258079678144</v>
+        <v>3.923169379476984</v>
       </c>
       <c r="D2" t="n">
-        <v>24.07088145884036</v>
+        <v>3.911518237061559</v>
       </c>
       <c r="E2" t="n">
-        <v>8.839006157271326</v>
+        <v>1.436338500556591</v>
       </c>
       <c r="F2" t="n">
-        <v>8.314430096034933</v>
+        <v>1.351094890605677</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.557467652108559</v>
+        <v>0.2530884934676409</v>
       </c>
       <c r="D3" t="n">
-        <v>2.93246471479236</v>
+        <v>0.4765255161537586</v>
       </c>
       <c r="E3" t="n">
-        <v>8.839006157271326</v>
+        <v>1.436338500556591</v>
       </c>
       <c r="F3" t="n">
-        <v>8.314430096034933</v>
+        <v>1.351094890605677</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.17977431975569</v>
+        <v>3.116713326960299</v>
       </c>
       <c r="D4" t="n">
-        <v>19.36005474828417</v>
+        <v>3.146008896596177</v>
       </c>
       <c r="E4" t="n">
-        <v>8.839006157271326</v>
+        <v>1.436338500556591</v>
       </c>
       <c r="F4" t="n">
-        <v>8.314430096034933</v>
+        <v>1.351094890605677</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.97749479407714</v>
+        <v>3.246342904037535</v>
       </c>
       <c r="D5" t="n">
-        <v>19.06710421928725</v>
+        <v>3.098404435634178</v>
       </c>
       <c r="E5" t="n">
-        <v>8.839006157271326</v>
+        <v>1.436338500556591</v>
       </c>
       <c r="F5" t="n">
-        <v>8.314430096034933</v>
+        <v>1.351094890605677</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.8211730174829</v>
+        <v>4.358440615340971</v>
       </c>
       <c r="D6" t="n">
-        <v>26.93848300822131</v>
+        <v>4.377503488835963</v>
       </c>
       <c r="E6" t="n">
-        <v>8.839006157271326</v>
+        <v>1.436338500556591</v>
       </c>
       <c r="F6" t="n">
-        <v>8.314430096034933</v>
+        <v>1.351094890605677</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
